--- a/CANDIDATES LIST.xlsx
+++ b/CANDIDATES LIST.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="258">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -217,6 +217,9 @@
     <t xml:space="preserve">SLB N.V.</t>
   </si>
   <si>
+    <t xml:space="preserve">Full Tier 1-3 scored 9/13/26: Composite 72.4, BUY. See Journal, Scoring row 50.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PYPL</t>
   </si>
   <si>
@@ -247,6 +250,9 @@
     <t xml:space="preserve">Medical Devices</t>
   </si>
   <si>
+    <t xml:space="preserve">Full Tier 1-3 scored 9/13/26: Composite 70.8, BUY. See Journal, Scoring row 49.</t>
+  </si>
+  <si>
     <t xml:space="preserve">AZN</t>
   </si>
   <si>
@@ -446,6 +452,9 @@
   </si>
   <si>
     <t xml:space="preserve">REIT - Specialty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Growth Consistency -15.2% CAGR is a mix of a deliberate fiber/small-cell divestiture (closed May 2026) AND genuine unresolved litigation: DISH allegedly defaulted on tower lease payments, Crown Castle terminated and is suing for over $3.5B, DISH counters with a force majeure claim already through an appeals court. A tower REIT thesis depends on durable, visible lease revenue -- this is live, unresolved uncertainty on exactly that. Rejected rather than scored further. See Journal.</t>
   </si>
   <si>
     <t xml:space="preserve">COLD</t>
@@ -2155,12 +2164,14 @@
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="N7" s="11" t="s">
         <v>31</v>
       </c>
@@ -2170,16 +2181,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C8,$N$3:$N$13,0)),0.25)</f>
@@ -2193,16 +2204,16 @@
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0</v>
@@ -2210,16 +2221,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C9,$N$3:$N$13,0)),0.25)</f>
@@ -2233,14 +2244,16 @@
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.0342</v>
@@ -2248,16 +2261,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C10,$N$3:$N$13,0)),0.25)</f>
@@ -2278,7 +2291,7 @@
       </c>
       <c r="K10" s="9"/>
       <c r="N10" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>0.0119</v>
@@ -2286,16 +2299,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C11,$N$3:$N$13,0)),0.25)</f>
@@ -2316,7 +2329,7 @@
       </c>
       <c r="K11" s="9"/>
       <c r="N11" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>0.0249</v>
@@ -2324,16 +2337,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C12,$N$3:$N$13,0)),0.25)</f>
@@ -2354,7 +2367,7 @@
       </c>
       <c r="K12" s="9"/>
       <c r="N12" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O12" s="12" t="n">
         <v>0.2586</v>
@@ -2362,16 +2375,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C13,$N$3:$N$13,0)),0.25)</f>
@@ -2392,7 +2405,7 @@
       </c>
       <c r="K13" s="9"/>
       <c r="N13" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O13" s="12" t="n">
         <v>0</v>
@@ -2400,16 +2413,16 @@
     </row>
     <row r="14" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C14,$N$3:$N$13,0)),0.25)</f>
@@ -2429,21 +2442,21 @@
         <v>46264</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C15,$N$3:$N$13,0)),0.25)</f>
@@ -2466,16 +2479,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C16,$N$3:$N$13,0)),0.25)</f>
@@ -2498,16 +2511,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E17" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C17,$N$3:$N$13,0)),0.25)</f>
@@ -2530,16 +2543,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C18,$N$3:$N$13,0)),0.25)</f>
@@ -2562,16 +2575,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C19,$N$3:$N$13,0)),0.25)</f>
@@ -2585,27 +2598,27 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E20" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C20,$N$3:$N$13,0)),0.25)</f>
@@ -2628,16 +2641,16 @@
     </row>
     <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E21" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C21,$N$3:$N$13,0)),0.25)</f>
@@ -2657,21 +2670,21 @@
         <v>46264</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C22,$N$3:$N$13,0)),0.25)</f>
@@ -2685,27 +2698,27 @@
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C23,$N$3:$N$13,0)),0.25)</f>
@@ -2725,21 +2738,21 @@
         <v>46264</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E24" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C24,$N$3:$N$13,0)),0.25)</f>
@@ -2759,21 +2772,21 @@
         <v>46244</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E25" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C25,$N$3:$N$13,0)),0.25)</f>
@@ -2793,21 +2806,21 @@
         <v>46244</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E26" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C26,$N$3:$N$13,0)),0.25)</f>
@@ -2827,21 +2840,21 @@
         <v>46244</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E27" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C27,$N$3:$N$13,0)),0.25)</f>
@@ -2864,16 +2877,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E28" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C28,$N$3:$N$13,0)),0.25)</f>
@@ -2896,16 +2909,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E29" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C29,$N$3:$N$13,0)),0.25)</f>
@@ -2928,16 +2941,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C30,$N$3:$N$13,0)),0.25)</f>
@@ -2951,25 +2964,27 @@
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K30" s="9"/>
+      <c r="K30" s="9" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E31" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C31,$N$3:$N$13,0)),0.25)</f>
@@ -2989,21 +3004,21 @@
         <v>46244</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E32" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C32,$N$3:$N$13,0)),0.25)</f>
@@ -3026,16 +3041,16 @@
     </row>
     <row r="33" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E33" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C33,$N$3:$N$13,0)),0.25)</f>
@@ -3055,21 +3070,21 @@
         <v>46264</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E34" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C34,$N$3:$N$13,0)),0.25)</f>
@@ -3089,21 +3104,21 @@
         <v>46264</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E35" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C35,$N$3:$N$13,0)),0.25)</f>
@@ -3123,21 +3138,21 @@
         <v>46244</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E36" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C36,$N$3:$N$13,0)),0.25)</f>
@@ -3157,21 +3172,21 @@
         <v>46264</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E37" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C37,$N$3:$N$13,0)),0.25)</f>
@@ -3194,16 +3209,16 @@
     </row>
     <row r="38" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E38" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C38,$N$3:$N$13,0)),0.25)</f>
@@ -3223,21 +3238,21 @@
         <v>46264</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E39" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C39,$N$3:$N$13,0)),0.25)</f>
@@ -3260,16 +3275,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E40" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C40,$N$3:$N$13,0)),0.25)</f>
@@ -3282,7 +3297,7 @@
         <v>28</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>33</v>
@@ -3294,16 +3309,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E41" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C41,$N$3:$N$13,0)),0.25)</f>
@@ -3316,7 +3331,7 @@
         <v>28</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>33</v>
@@ -3328,16 +3343,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C42,$N$3:$N$13,0)),0.25)</f>
@@ -3350,7 +3365,7 @@
         <v>28</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>33</v>
@@ -3362,16 +3377,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E43" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C43,$N$3:$N$13,0)),0.25)</f>
@@ -3384,7 +3399,7 @@
         <v>28</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>33</v>
@@ -3396,16 +3411,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E44" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C44,$N$3:$N$13,0)),0.25)</f>
@@ -3418,7 +3433,7 @@
         <v>28</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>33</v>
@@ -3430,16 +3445,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E45" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C45,$N$3:$N$13,0)),0.25)</f>
@@ -3452,7 +3467,7 @@
         <v>28</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>33</v>
@@ -3464,16 +3479,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E46" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C46,$N$3:$N$13,0)),0.25)</f>
@@ -3486,7 +3501,7 @@
         <v>28</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>33</v>
@@ -3498,10 +3513,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>31</v>
@@ -3520,7 +3535,7 @@
         <v>28</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>33</v>
@@ -3532,16 +3547,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E48" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C48,$N$3:$N$13,0)),0.25)</f>
@@ -3554,7 +3569,7 @@
         <v>28</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>33</v>
@@ -3566,16 +3581,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E49" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C49,$N$3:$N$13,0)),0.25)</f>
@@ -3588,7 +3603,7 @@
         <v>28</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>33</v>
@@ -3600,16 +3615,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E50" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C50,$N$3:$N$13,0)),0.25)</f>
@@ -3622,7 +3637,7 @@
         <v>28</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>33</v>
@@ -3634,16 +3649,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E51" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C51,$N$3:$N$13,0)),0.25)</f>
@@ -3656,10 +3671,10 @@
         <v>28</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>46244</v>
@@ -3668,16 +3683,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E52" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C52,$N$3:$N$13,0)),0.25)</f>
@@ -3690,10 +3705,10 @@
         <v>28</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>46244</v>
@@ -3702,16 +3717,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E53" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C53,$N$3:$N$13,0)),0.25)</f>
@@ -3724,10 +3739,10 @@
         <v>28</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>46244</v>
@@ -3736,16 +3751,16 @@
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E54" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C54,$N$3:$N$13,0)),0.25)</f>
@@ -3758,30 +3773,30 @@
         <v>28</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E55" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C55,$N$3:$N$13,0)),0.25)</f>
@@ -3794,30 +3809,30 @@
         <v>28</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E56" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C56,$N$3:$N$13,0)),0.25)</f>
@@ -3830,10 +3845,10 @@
         <v>28</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>46244</v>
@@ -3842,16 +3857,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E57" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C57,$N$3:$N$13,0)),0.25)</f>
@@ -3864,10 +3879,10 @@
         <v>28</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>46244</v>
@@ -3876,16 +3891,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C58,$N$3:$N$13,0)),0.25)</f>
@@ -3898,10 +3913,10 @@
         <v>28</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>46244</v>
@@ -3910,16 +3925,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E59" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C59,$N$3:$N$13,0)),0.25)</f>
@@ -3932,30 +3947,30 @@
         <v>28</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E60" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C60,$N$3:$N$13,0)),0.25)</f>
@@ -3968,10 +3983,10 @@
         <v>28</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>46244</v>
@@ -3980,16 +3995,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E61" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C61,$N$3:$N$13,0)),0.25)</f>
@@ -4002,10 +4017,10 @@
         <v>28</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>46244</v>
@@ -4014,16 +4029,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E62" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C62,$N$3:$N$13,0)),0.25)</f>
@@ -4036,10 +4051,10 @@
         <v>28</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>46244</v>
@@ -4048,16 +4063,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E63" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C63,$N$3:$N$13,0)),0.25)</f>
@@ -4070,10 +4085,10 @@
         <v>28</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>46244</v>
@@ -4082,10 +4097,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>31</v>
@@ -4104,10 +4119,10 @@
         <v>28</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>46244</v>
@@ -4116,10 +4131,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>31</v>
@@ -4138,10 +4153,10 @@
         <v>28</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>46244</v>
@@ -4150,16 +4165,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E66" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C66,$N$3:$N$13,0)),0.25)</f>
@@ -4172,10 +4187,10 @@
         <v>28</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>46244</v>
@@ -4275,79 +4290,79 @@
         <v>14</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>31</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="S1" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="U1" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V1" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="W1" s="20" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Z1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" s="21" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4388,63 +4403,63 @@
         <v>3</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" s="21" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="32" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N3" s="28"/>
       <c r="O3" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P3" s="30"/>
       <c r="Q3" s="27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R3" s="28"/>
       <c r="S3" s="29" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="T3" s="30"/>
       <c r="U3" s="27" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="V3" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="W3" s="33"/>
       <c r="Z3" s="25" t="s">
@@ -4454,133 +4469,133 @@
         <v>2</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="36" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P4" s="37"/>
       <c r="Q4" s="34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="R4" s="35"/>
       <c r="S4" s="36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="T4" s="37"/>
       <c r="U4" s="38" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Z4" s="25" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AA4" s="26" t="n">
         <v>10</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="37"/>
       <c r="E5" s="38" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K5" s="36"/>
       <c r="L5" s="37"/>
       <c r="M5" s="34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N5" s="35"/>
       <c r="O5" s="36" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P5" s="37"/>
       <c r="Q5" s="34"/>
       <c r="R5" s="35"/>
       <c r="S5" s="36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="T5" s="37"/>
       <c r="U5" s="34"/>
       <c r="V5" s="35"/>
       <c r="Z5" s="25" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AA5" s="26" t="n">
         <v>4</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4589,40 +4604,40 @@
       <c r="C6" s="36"/>
       <c r="D6" s="37"/>
       <c r="E6" s="34" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K6" s="36"/>
       <c r="L6" s="37"/>
       <c r="M6" s="34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N6" s="35"/>
       <c r="O6" s="36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P6" s="37"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="35"/>
       <c r="S6" s="38" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="T6" s="40" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="U6" s="34"/>
       <c r="V6" s="35"/>
@@ -4633,7 +4648,7 @@
         <v>6</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4642,10 +4657,10 @@
       <c r="C7" s="36"/>
       <c r="D7" s="37"/>
       <c r="E7" s="41" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="37"/>
@@ -4656,29 +4671,29 @@
       <c r="K7" s="36"/>
       <c r="L7" s="37"/>
       <c r="M7" s="34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N7" s="35"/>
       <c r="O7" s="36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P7" s="37"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35"/>
       <c r="S7" s="36" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="34"/>
       <c r="V7" s="35"/>
       <c r="Z7" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA7" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4688,7 +4703,7 @@
       <c r="D8" s="37"/>
       <c r="E8" s="43"/>
       <c r="F8" s="44" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="37"/>
@@ -4699,11 +4714,11 @@
       <c r="K8" s="36"/>
       <c r="L8" s="37"/>
       <c r="M8" s="34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N8" s="35"/>
       <c r="O8" s="36" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P8" s="37"/>
       <c r="Q8" s="34"/>
@@ -4713,13 +4728,13 @@
       <c r="U8" s="34"/>
       <c r="V8" s="35"/>
       <c r="Z8" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="26" t="n">
         <v>9</v>
       </c>
       <c r="AB8" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4728,10 +4743,10 @@
       <c r="C9" s="36"/>
       <c r="D9" s="37"/>
       <c r="E9" s="45" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="37"/>
@@ -4740,11 +4755,11 @@
       <c r="K9" s="36"/>
       <c r="L9" s="37"/>
       <c r="M9" s="34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N9" s="35"/>
       <c r="O9" s="36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="34"/>
@@ -4754,13 +4769,13 @@
       <c r="U9" s="34"/>
       <c r="V9" s="35"/>
       <c r="Z9" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA9" s="26" t="n">
         <v>8</v>
       </c>
       <c r="AB9" s="25" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4769,10 +4784,10 @@
       <c r="C10" s="36"/>
       <c r="D10" s="37"/>
       <c r="E10" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G10" s="36"/>
       <c r="H10" s="37"/>
@@ -4781,11 +4796,11 @@
       <c r="K10" s="36"/>
       <c r="L10" s="37"/>
       <c r="M10" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N10" s="35"/>
       <c r="O10" s="36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P10" s="37"/>
       <c r="Q10" s="34"/>
@@ -4795,13 +4810,13 @@
       <c r="U10" s="34"/>
       <c r="V10" s="35"/>
       <c r="Z10" s="25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA10" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4810,10 +4825,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="37"/>
       <c r="E11" s="34" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G11" s="36"/>
       <c r="H11" s="37"/>
@@ -4822,7 +4837,7 @@
       <c r="K11" s="36"/>
       <c r="L11" s="37"/>
       <c r="M11" s="34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
@@ -4834,13 +4849,13 @@
       <c r="U11" s="34"/>
       <c r="V11" s="35"/>
       <c r="Z11" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA11" s="26" t="n">
         <v>5</v>
       </c>
       <c r="AB11" s="25" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4850,7 +4865,7 @@
       <c r="D12" s="37"/>
       <c r="E12" s="43"/>
       <c r="F12" s="47" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="37"/>
@@ -4859,7 +4874,7 @@
       <c r="K12" s="36"/>
       <c r="L12" s="37"/>
       <c r="M12" s="34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
@@ -4871,13 +4886,13 @@
       <c r="U12" s="34"/>
       <c r="V12" s="35"/>
       <c r="Z12" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA12" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB12" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4886,10 +4901,10 @@
       <c r="C13" s="36"/>
       <c r="D13" s="37"/>
       <c r="E13" s="45" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G13" s="36"/>
       <c r="H13" s="37"/>
@@ -4908,13 +4923,13 @@
       <c r="U13" s="34"/>
       <c r="V13" s="35"/>
       <c r="Z13" s="48" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AA13" s="49" t="n">
         <v>1</v>
       </c>
       <c r="AB13" s="48" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4923,10 +4938,10 @@
       <c r="C14" s="36"/>
       <c r="D14" s="37"/>
       <c r="E14" s="34" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G14" s="36"/>
       <c r="H14" s="37"/>
@@ -4951,10 +4966,10 @@
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
       <c r="E15" s="54" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G15" s="52"/>
       <c r="H15" s="53"/>
@@ -5132,15 +5147,15 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E19" s="59" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E20" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="V20" s="60" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="W20" s="61" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"PASS")</f>
@@ -5153,7 +5168,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V21" s="60" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W21" s="63" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"Avoid")</f>
@@ -5166,7 +5181,7 @@
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V22" s="60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="W22" s="65" t="n">
         <f aca="false">SUM(W20:W21)</f>

--- a/CANDIDATES LIST.xlsx
+++ b/CANDIDATES LIST.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="262">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -331,6 +331,12 @@
     <t xml:space="preserve">Healthcare Plans</t>
   </si>
   <si>
+    <t xml:space="preserve">Watch - Pending Litigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 9/30/26: ~3.33 quant-only (no severe outlier -- fcf_yield 3, rev growth 4, fcf margin 2, valuation 3, analyst consensus 5, technical 4, volume 2, relative strength 4, ROIC 3), clears the floor on its own. But a Fidelity info-tab scan (new practice, see Journal 9/30/26) surfaced real qualitative red flags the quant screen can't see: Equity Summary Score genuinely Bearish (1.5/10, not just mixed), and active litigation -- judge denied in part UnitedHealth's motion to dismiss a CalPERS suit the same day this was screened. TTM EPS -32.67% vs industry +8.94% (real trailing decline), though the most recent single quarter beat and grew faster than industry (+61.5% vs +51.1%), suggesting possible stabilization. Alan's call: flag to score further only after the litigation situation settles -- not a floor-failure rejection like XRAY/GXO/CCI, just not proceeding to full Tier 1-3 now. Revisit on a clearer CalPERS resolution or after Q3 earnings (10/13/26). See Journal row 69.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VEEV</t>
   </si>
   <si>
@@ -476,6 +482,12 @@
   </si>
   <si>
     <t xml:space="preserve">Information Technology Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watch - Pending Earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 9/30/26: ~2.875 quant-only (marginal -- dragged down almost entirely by relative_strength=1, blended -34.7% vs SPY; otherwise fine -- fcf_yield 4, valuation 4 discount, margin stable 3). A Fidelity info-tab scan (new practice, see Journal 9/30/26) shows the opposite sentiment: Equity Summary Score Very Bullish (9.4/10), positive news flow (UBS: on pace to more than double bookings), P/E ~40% of the IT-services industry average. GAAP EPS (TTM) and P/E both show '--' (likely a large one-time charge -- the adjusted quarterly EPS chart looks normal with consistent beats). Reports Q4 earnings 10/1/26 -- the next trading day as of this screen. Alan's call: hold open, no score or further screening until after that print -- anything decided today would be immediately overtaken. See Journal row 69.</t>
   </si>
   <si>
     <t xml:space="preserve">ALAB</t>
@@ -2534,25 +2546,27 @@
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C18,$N$3:$N$13,0)),0.25)</f>
@@ -2575,10 +2589,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>51</v>
@@ -2604,21 +2618,21 @@
         <v>46244</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E20" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C20,$N$3:$N$13,0)),0.25)</f>
@@ -2641,16 +2655,16 @@
     </row>
     <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C21,$N$3:$N$13,0)),0.25)</f>
@@ -2670,21 +2684,21 @@
         <v>46264</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C22,$N$3:$N$13,0)),0.25)</f>
@@ -2704,21 +2718,21 @@
         <v>46244</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E23" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C23,$N$3:$N$13,0)),0.25)</f>
@@ -2738,21 +2752,21 @@
         <v>46264</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C24,$N$3:$N$13,0)),0.25)</f>
@@ -2772,21 +2786,21 @@
         <v>46244</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E25" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C25,$N$3:$N$13,0)),0.25)</f>
@@ -2806,21 +2820,21 @@
         <v>46244</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C26,$N$3:$N$13,0)),0.25)</f>
@@ -2840,21 +2854,21 @@
         <v>46244</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E27" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C27,$N$3:$N$13,0)),0.25)</f>
@@ -2877,16 +2891,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E28" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C28,$N$3:$N$13,0)),0.25)</f>
@@ -2909,16 +2923,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E29" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C29,$N$3:$N$13,0)),0.25)</f>
@@ -2941,16 +2955,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C30,$N$3:$N$13,0)),0.25)</f>
@@ -2970,21 +2984,21 @@
         <v>46244</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E31" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C31,$N$3:$N$13,0)),0.25)</f>
@@ -3004,21 +3018,21 @@
         <v>46244</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E32" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C32,$N$3:$N$13,0)),0.25)</f>
@@ -3032,25 +3046,27 @@
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K32" s="9"/>
+      <c r="K32" s="9" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E33" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C33,$N$3:$N$13,0)),0.25)</f>
@@ -3070,21 +3086,21 @@
         <v>46264</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E34" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C34,$N$3:$N$13,0)),0.25)</f>
@@ -3104,21 +3120,21 @@
         <v>46264</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E35" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C35,$N$3:$N$13,0)),0.25)</f>
@@ -3138,21 +3154,21 @@
         <v>46244</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E36" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C36,$N$3:$N$13,0)),0.25)</f>
@@ -3172,21 +3188,21 @@
         <v>46264</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E37" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C37,$N$3:$N$13,0)),0.25)</f>
@@ -3209,16 +3225,16 @@
     </row>
     <row r="38" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E38" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C38,$N$3:$N$13,0)),0.25)</f>
@@ -3238,21 +3254,21 @@
         <v>46264</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E39" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C39,$N$3:$N$13,0)),0.25)</f>
@@ -3275,16 +3291,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E40" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C40,$N$3:$N$13,0)),0.25)</f>
@@ -3297,7 +3313,7 @@
         <v>28</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>33</v>
@@ -3309,16 +3325,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E41" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C41,$N$3:$N$13,0)),0.25)</f>
@@ -3331,7 +3347,7 @@
         <v>28</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>33</v>
@@ -3343,16 +3359,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E42" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C42,$N$3:$N$13,0)),0.25)</f>
@@ -3365,7 +3381,7 @@
         <v>28</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>33</v>
@@ -3377,16 +3393,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E43" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C43,$N$3:$N$13,0)),0.25)</f>
@@ -3399,7 +3415,7 @@
         <v>28</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>33</v>
@@ -3411,16 +3427,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E44" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C44,$N$3:$N$13,0)),0.25)</f>
@@ -3433,7 +3449,7 @@
         <v>28</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>33</v>
@@ -3445,16 +3461,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E45" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C45,$N$3:$N$13,0)),0.25)</f>
@@ -3467,7 +3483,7 @@
         <v>28</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>33</v>
@@ -3479,16 +3495,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E46" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C46,$N$3:$N$13,0)),0.25)</f>
@@ -3501,7 +3517,7 @@
         <v>28</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>33</v>
@@ -3513,10 +3529,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>31</v>
@@ -3535,7 +3551,7 @@
         <v>28</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>33</v>
@@ -3547,10 +3563,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>45</v>
@@ -3569,7 +3585,7 @@
         <v>28</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>33</v>
@@ -3581,16 +3597,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E49" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C49,$N$3:$N$13,0)),0.25)</f>
@@ -3603,7 +3619,7 @@
         <v>28</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>33</v>
@@ -3615,16 +3631,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E50" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C50,$N$3:$N$13,0)),0.25)</f>
@@ -3637,7 +3653,7 @@
         <v>28</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>33</v>
@@ -3649,16 +3665,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E51" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C51,$N$3:$N$13,0)),0.25)</f>
@@ -3671,7 +3687,7 @@
         <v>28</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>47</v>
@@ -3683,16 +3699,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E52" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C52,$N$3:$N$13,0)),0.25)</f>
@@ -3705,7 +3721,7 @@
         <v>28</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>47</v>
@@ -3717,16 +3733,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E53" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C53,$N$3:$N$13,0)),0.25)</f>
@@ -3739,7 +3755,7 @@
         <v>28</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>47</v>
@@ -3751,16 +3767,16 @@
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E54" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C54,$N$3:$N$13,0)),0.25)</f>
@@ -3773,7 +3789,7 @@
         <v>28</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>47</v>
@@ -3782,21 +3798,21 @@
         <v>46244</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E55" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C55,$N$3:$N$13,0)),0.25)</f>
@@ -3809,7 +3825,7 @@
         <v>28</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>47</v>
@@ -3818,21 +3834,21 @@
         <v>46244</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E56" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C56,$N$3:$N$13,0)),0.25)</f>
@@ -3845,7 +3861,7 @@
         <v>28</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>47</v>
@@ -3857,16 +3873,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E57" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C57,$N$3:$N$13,0)),0.25)</f>
@@ -3879,7 +3895,7 @@
         <v>28</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>47</v>
@@ -3891,16 +3907,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E58" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C58,$N$3:$N$13,0)),0.25)</f>
@@ -3913,7 +3929,7 @@
         <v>28</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>47</v>
@@ -3925,16 +3941,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E59" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C59,$N$3:$N$13,0)),0.25)</f>
@@ -3947,7 +3963,7 @@
         <v>28</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>47</v>
@@ -3956,21 +3972,21 @@
         <v>46244</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E60" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C60,$N$3:$N$13,0)),0.25)</f>
@@ -3983,7 +3999,7 @@
         <v>28</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>47</v>
@@ -3995,16 +4011,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E61" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C61,$N$3:$N$13,0)),0.25)</f>
@@ -4017,7 +4033,7 @@
         <v>28</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>47</v>
@@ -4029,16 +4045,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E62" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C62,$N$3:$N$13,0)),0.25)</f>
@@ -4051,7 +4067,7 @@
         <v>28</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>47</v>
@@ -4063,16 +4079,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E63" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C63,$N$3:$N$13,0)),0.25)</f>
@@ -4085,7 +4101,7 @@
         <v>28</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>47</v>
@@ -4097,10 +4113,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>31</v>
@@ -4119,7 +4135,7 @@
         <v>28</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>47</v>
@@ -4131,10 +4147,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>31</v>
@@ -4153,7 +4169,7 @@
         <v>28</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>47</v>
@@ -4165,16 +4181,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E66" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C66,$N$3:$N$13,0)),0.25)</f>
@@ -4187,7 +4203,7 @@
         <v>28</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>47</v>
@@ -4290,79 +4306,79 @@
         <v>14</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>31</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K1" s="18" t="s">
         <v>45</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M1" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>57</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q1" s="16" t="s">
         <v>61</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="S1" s="18" t="s">
         <v>64</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="U1" s="16" t="s">
         <v>68</v>
       </c>
       <c r="V1" s="17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="W1" s="20" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" s="21" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4403,37 +4419,37 @@
         <v>3</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" s="21" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C3" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="30" t="s">
         <v>186</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>182</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="32" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K3" s="29" t="s">
         <v>43</v>
@@ -4444,22 +4460,22 @@
       </c>
       <c r="N3" s="28"/>
       <c r="O3" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P3" s="30"/>
       <c r="Q3" s="27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R3" s="28"/>
       <c r="S3" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="T3" s="30"/>
       <c r="U3" s="27" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="V3" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="W3" s="33"/>
       <c r="Z3" s="25" t="s">
@@ -4469,106 +4485,106 @@
         <v>2</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>153</v>
-      </c>
       <c r="G4" s="36" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="36" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P4" s="37"/>
       <c r="Q4" s="34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R4" s="35"/>
       <c r="S4" s="36" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="T4" s="37"/>
       <c r="U4" s="38" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Z4" s="25" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AA4" s="26" t="n">
         <v>10</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="37"/>
       <c r="E5" s="38" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K5" s="36"/>
       <c r="L5" s="37"/>
@@ -4577,25 +4593,25 @@
       </c>
       <c r="N5" s="35"/>
       <c r="O5" s="36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P5" s="37"/>
       <c r="Q5" s="34"/>
       <c r="R5" s="35"/>
       <c r="S5" s="36" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="T5" s="37"/>
       <c r="U5" s="34"/>
       <c r="V5" s="35"/>
       <c r="Z5" s="25" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AA5" s="26" t="n">
         <v>4</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4604,22 +4620,22 @@
       <c r="C6" s="36"/>
       <c r="D6" s="37"/>
       <c r="E6" s="34" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K6" s="36"/>
       <c r="L6" s="37"/>
@@ -4628,16 +4644,16 @@
       </c>
       <c r="N6" s="35"/>
       <c r="O6" s="36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P6" s="37"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="35"/>
       <c r="S6" s="38" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="T6" s="40" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="U6" s="34"/>
       <c r="V6" s="35"/>
@@ -4648,7 +4664,7 @@
         <v>6</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4657,10 +4673,10 @@
       <c r="C7" s="36"/>
       <c r="D7" s="37"/>
       <c r="E7" s="41" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="37"/>
@@ -4675,13 +4691,13 @@
       </c>
       <c r="N7" s="35"/>
       <c r="O7" s="36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P7" s="37"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35"/>
       <c r="S7" s="36" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="34"/>
@@ -4693,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4703,7 +4719,7 @@
       <c r="D8" s="37"/>
       <c r="E8" s="43"/>
       <c r="F8" s="44" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="37"/>
@@ -4718,7 +4734,7 @@
       </c>
       <c r="N8" s="35"/>
       <c r="O8" s="36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P8" s="37"/>
       <c r="Q8" s="34"/>
@@ -4734,7 +4750,7 @@
         <v>9</v>
       </c>
       <c r="AB8" s="25" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4743,10 +4759,10 @@
       <c r="C9" s="36"/>
       <c r="D9" s="37"/>
       <c r="E9" s="45" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="37"/>
@@ -4759,7 +4775,7 @@
       </c>
       <c r="N9" s="35"/>
       <c r="O9" s="36" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="34"/>
@@ -4775,7 +4791,7 @@
         <v>8</v>
       </c>
       <c r="AB9" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4784,10 +4800,10 @@
       <c r="C10" s="36"/>
       <c r="D10" s="37"/>
       <c r="E10" s="34" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G10" s="36"/>
       <c r="H10" s="37"/>
@@ -4800,7 +4816,7 @@
       </c>
       <c r="N10" s="35"/>
       <c r="O10" s="36" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P10" s="37"/>
       <c r="Q10" s="34"/>
@@ -4816,7 +4832,7 @@
         <v>2</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4825,10 +4841,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="37"/>
       <c r="E11" s="34" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G11" s="36"/>
       <c r="H11" s="37"/>
@@ -4837,7 +4853,7 @@
       <c r="K11" s="36"/>
       <c r="L11" s="37"/>
       <c r="M11" s="34" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
@@ -4855,7 +4871,7 @@
         <v>5</v>
       </c>
       <c r="AB11" s="25" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4865,7 +4881,7 @@
       <c r="D12" s="37"/>
       <c r="E12" s="43"/>
       <c r="F12" s="47" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="37"/>
@@ -4874,7 +4890,7 @@
       <c r="K12" s="36"/>
       <c r="L12" s="37"/>
       <c r="M12" s="34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
@@ -4892,7 +4908,7 @@
         <v>2</v>
       </c>
       <c r="AB12" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4901,10 +4917,10 @@
       <c r="C13" s="36"/>
       <c r="D13" s="37"/>
       <c r="E13" s="45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G13" s="36"/>
       <c r="H13" s="37"/>
@@ -4923,13 +4939,13 @@
       <c r="U13" s="34"/>
       <c r="V13" s="35"/>
       <c r="Z13" s="48" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AA13" s="49" t="n">
         <v>1</v>
       </c>
       <c r="AB13" s="48" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4938,10 +4954,10 @@
       <c r="C14" s="36"/>
       <c r="D14" s="37"/>
       <c r="E14" s="34" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G14" s="36"/>
       <c r="H14" s="37"/>
@@ -4966,10 +4982,10 @@
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
       <c r="E15" s="54" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G15" s="52"/>
       <c r="H15" s="53"/>
@@ -5147,15 +5163,15 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E19" s="59" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E20" s="13" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="V20" s="60" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="W20" s="61" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"PASS")</f>
@@ -5168,7 +5184,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V21" s="60" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="W21" s="63" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"Avoid")</f>
@@ -5181,7 +5197,7 @@
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V22" s="60" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W22" s="65" t="n">
         <f aca="false">SUM(W20:W21)</f>

--- a/CANDIDATES LIST.xlsx
+++ b/CANDIDATES LIST.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="265">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -178,6 +178,12 @@
     <t xml:space="preserve">Darryl</t>
   </si>
   <si>
+    <t xml:space="preserve">Ready for Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 9/30/26: ~3.67 quant-only (strong -- fcf_yield 4, rev growth 4, fcf margin 4 expanding, valuation 4 discount, analyst consensus 5, technical 4, ROIC 5 [44.6% vs WACC 11.1%, +33.5pp spread]; only weak spot relative_strength=1, blended -29.7% vs SPY). Same fundamentals-strong-but-price-lagging pattern as ACN -- ran the Fidelity scan on it specifically. Unlike ACN/ADBE/UNH, this one reinforced rather than undercut the quant read: Equity Summary Score Bullish (7.2/10), zero Sell ratings across 6 firms, Evercore ISI raised its price target to $700 on 9/29, short interest declining (6.12M -&gt; 4.52M). Price weakness reads as giving back part of a large 2yr (+32%) / 5yr (+121%) run after a Q2 EPS miss, not a structural deterioration -- meaningfully different pattern from ADBE's multi-year decline. Cleared to Ready for Tier 1; full Tier 1-3 scoring not done yet (separate pass, like ABT/SLB). Reports Q3 earnings 10/22/26. See Journal row 70.</t>
+  </si>
+  <si>
     <t xml:space="preserve">KGS</t>
   </si>
   <si>
@@ -190,9 +196,6 @@
     <t xml:space="preserve">Oil &amp; Gas Equipment &amp; Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Ready for Tier 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fresh Tier 1 quant screen 9/11/26: FCF Yield=4, Rev Growth=4, FCF Margin=4 (Tier1 Wtd Avg=4.0 on known indicators). Moat/Rev Visibility not yet assessed (Part 12, qualitative). Added to Scoring (row 48) and Monitor &amp; Recheck Triggers as Watch List.</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t xml:space="preserve">Pfizer Inc.</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 9/30/26: ~2.56 quant-only, decisive floor failure -- two indicators at the literal floor: revenue_growth_consistency=1 (negative CAGR -14.8%) and roic_vs_wacc=1 (ROIC 5.1% vs WACC 6.2%, actually value-destroying, spread -1.1pp). Same territory as GXO's rejection. Analyst consensus also weak (36% buy-equivalent, 7% negative). Rejected -- fundamental, not a data-quality artifact. See Journal row 70.</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNH</t>
   </si>
   <si>
@@ -449,6 +455,9 @@
   </si>
   <si>
     <t xml:space="preserve">United Parcel Service, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 9/30/26: ~2.44 quant-only, decisive floor failure -- two indicators at the literal floor: revenue_growth_consistency=1 (negative CAGR -4.0%) and technical_trend=1 (200w MA below, MACD not ok, Supertrend bearish -- broadly negative across the board). Same territory as GXO's rejection. Rejected -- fundamental, not a data-quality artifact. See Journal row 70.</t>
   </si>
   <si>
     <t xml:space="preserve">CCI</t>
@@ -2060,12 +2069,14 @@
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K4" s="9"/>
+      <c r="K4" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="N4" s="11" t="s">
         <v>22</v>
       </c>
@@ -2075,16 +2086,16 @@
     </row>
     <row r="5" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C5,$N$3:$N$13,0)),0.25)</f>
@@ -2098,16 +2109,16 @@
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>46264</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" s="12" t="n">
         <v>0</v>
@@ -2115,16 +2126,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C6,$N$3:$N$13,0)),0.25)</f>
@@ -2145,7 +2156,7 @@
       </c>
       <c r="K6" s="9"/>
       <c r="N6" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>0</v>
@@ -2153,16 +2164,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C7,$N$3:$N$13,0)),0.25)</f>
@@ -2176,16 +2187,16 @@
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>46244</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>46244</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0</v>
@@ -2193,16 +2204,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C8,$N$3:$N$13,0)),0.25)</f>
@@ -2216,16 +2227,16 @@
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0</v>
@@ -2233,16 +2244,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C9,$N$3:$N$13,0)),0.25)</f>
@@ -2256,16 +2267,16 @@
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.0342</v>
@@ -2273,16 +2284,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C10,$N$3:$N$13,0)),0.25)</f>
@@ -2303,7 +2314,7 @@
       </c>
       <c r="K10" s="9"/>
       <c r="N10" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>0.0119</v>
@@ -2311,16 +2322,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C11,$N$3:$N$13,0)),0.25)</f>
@@ -2341,7 +2352,7 @@
       </c>
       <c r="K11" s="9"/>
       <c r="N11" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>0.0249</v>
@@ -2349,16 +2360,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C12,$N$3:$N$13,0)),0.25)</f>
@@ -2379,7 +2390,7 @@
       </c>
       <c r="K12" s="9"/>
       <c r="N12" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O12" s="12" t="n">
         <v>0.2586</v>
@@ -2387,16 +2398,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C13,$N$3:$N$13,0)),0.25)</f>
@@ -2417,7 +2428,7 @@
       </c>
       <c r="K13" s="9"/>
       <c r="N13" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O13" s="12" t="n">
         <v>0</v>
@@ -2425,16 +2436,16 @@
     </row>
     <row r="14" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C14,$N$3:$N$13,0)),0.25)</f>
@@ -2454,21 +2465,21 @@
         <v>46264</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C15,$N$3:$N$13,0)),0.25)</f>
@@ -2491,16 +2502,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C16,$N$3:$N$13,0)),0.25)</f>
@@ -2514,25 +2525,27 @@
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K16" s="9"/>
+      <c r="K16" s="9" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C17,$N$3:$N$13,0)),0.25)</f>
@@ -2546,27 +2559,27 @@
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C18,$N$3:$N$13,0)),0.25)</f>
@@ -2589,16 +2602,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C19,$N$3:$N$13,0)),0.25)</f>
@@ -2612,27 +2625,27 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C20,$N$3:$N$13,0)),0.25)</f>
@@ -2655,16 +2668,16 @@
     </row>
     <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C21,$N$3:$N$13,0)),0.25)</f>
@@ -2684,21 +2697,21 @@
         <v>46264</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C22,$N$3:$N$13,0)),0.25)</f>
@@ -2712,27 +2725,27 @@
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E23" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C23,$N$3:$N$13,0)),0.25)</f>
@@ -2752,21 +2765,21 @@
         <v>46264</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E24" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C24,$N$3:$N$13,0)),0.25)</f>
@@ -2786,21 +2799,21 @@
         <v>46244</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E25" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C25,$N$3:$N$13,0)),0.25)</f>
@@ -2820,21 +2833,21 @@
         <v>46244</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E26" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C26,$N$3:$N$13,0)),0.25)</f>
@@ -2854,21 +2867,21 @@
         <v>46244</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E27" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C27,$N$3:$N$13,0)),0.25)</f>
@@ -2891,16 +2904,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E28" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C28,$N$3:$N$13,0)),0.25)</f>
@@ -2923,16 +2936,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E29" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C29,$N$3:$N$13,0)),0.25)</f>
@@ -2946,25 +2959,27 @@
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="K29" s="9"/>
+      <c r="K29" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E30" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C30,$N$3:$N$13,0)),0.25)</f>
@@ -2978,27 +2993,27 @@
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E31" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C31,$N$3:$N$13,0)),0.25)</f>
@@ -3018,21 +3033,21 @@
         <v>46244</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E32" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C32,$N$3:$N$13,0)),0.25)</f>
@@ -3046,27 +3061,27 @@
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E33" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C33,$N$3:$N$13,0)),0.25)</f>
@@ -3086,21 +3101,21 @@
         <v>46264</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E34" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C34,$N$3:$N$13,0)),0.25)</f>
@@ -3120,21 +3135,21 @@
         <v>46264</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E35" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C35,$N$3:$N$13,0)),0.25)</f>
@@ -3154,21 +3169,21 @@
         <v>46244</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E36" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C36,$N$3:$N$13,0)),0.25)</f>
@@ -3188,21 +3203,21 @@
         <v>46264</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E37" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C37,$N$3:$N$13,0)),0.25)</f>
@@ -3225,16 +3240,16 @@
     </row>
     <row r="38" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E38" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C38,$N$3:$N$13,0)),0.25)</f>
@@ -3254,21 +3269,21 @@
         <v>46264</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E39" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C39,$N$3:$N$13,0)),0.25)</f>
@@ -3291,16 +3306,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E40" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C40,$N$3:$N$13,0)),0.25)</f>
@@ -3313,10 +3328,10 @@
         <v>28</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>46244</v>
@@ -3325,16 +3340,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E41" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C41,$N$3:$N$13,0)),0.25)</f>
@@ -3347,10 +3362,10 @@
         <v>28</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>46244</v>
@@ -3359,16 +3374,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E42" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C42,$N$3:$N$13,0)),0.25)</f>
@@ -3381,10 +3396,10 @@
         <v>28</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>46244</v>
@@ -3393,16 +3408,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E43" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C43,$N$3:$N$13,0)),0.25)</f>
@@ -3415,10 +3430,10 @@
         <v>28</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>46244</v>
@@ -3427,16 +3442,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E44" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C44,$N$3:$N$13,0)),0.25)</f>
@@ -3449,10 +3464,10 @@
         <v>28</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>46244</v>
@@ -3461,16 +3476,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E45" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C45,$N$3:$N$13,0)),0.25)</f>
@@ -3483,10 +3498,10 @@
         <v>28</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>46244</v>
@@ -3495,16 +3510,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E46" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C46,$N$3:$N$13,0)),0.25)</f>
@@ -3517,10 +3532,10 @@
         <v>28</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>46244</v>
@@ -3529,16 +3544,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E47" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C47,$N$3:$N$13,0)),0.25)</f>
@@ -3551,10 +3566,10 @@
         <v>28</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>46244</v>
@@ -3563,16 +3578,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E48" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C48,$N$3:$N$13,0)),0.25)</f>
@@ -3585,10 +3600,10 @@
         <v>28</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>46244</v>
@@ -3597,16 +3612,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E49" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C49,$N$3:$N$13,0)),0.25)</f>
@@ -3619,10 +3634,10 @@
         <v>28</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>46244</v>
@@ -3631,16 +3646,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E50" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C50,$N$3:$N$13,0)),0.25)</f>
@@ -3653,10 +3668,10 @@
         <v>28</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>46244</v>
@@ -3665,16 +3680,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E51" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C51,$N$3:$N$13,0)),0.25)</f>
@@ -3687,10 +3702,10 @@
         <v>28</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>46244</v>
@@ -3699,16 +3714,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E52" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C52,$N$3:$N$13,0)),0.25)</f>
@@ -3721,10 +3736,10 @@
         <v>28</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>46244</v>
@@ -3733,16 +3748,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E53" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C53,$N$3:$N$13,0)),0.25)</f>
@@ -3755,10 +3770,10 @@
         <v>28</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>46244</v>
@@ -3767,16 +3782,16 @@
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E54" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C54,$N$3:$N$13,0)),0.25)</f>
@@ -3789,30 +3804,30 @@
         <v>28</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E55" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C55,$N$3:$N$13,0)),0.25)</f>
@@ -3825,30 +3840,30 @@
         <v>28</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E56" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C56,$N$3:$N$13,0)),0.25)</f>
@@ -3861,10 +3876,10 @@
         <v>28</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>46244</v>
@@ -3873,16 +3888,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E57" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C57,$N$3:$N$13,0)),0.25)</f>
@@ -3895,10 +3910,10 @@
         <v>28</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>46244</v>
@@ -3907,16 +3922,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E58" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C58,$N$3:$N$13,0)),0.25)</f>
@@ -3929,10 +3944,10 @@
         <v>28</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>46244</v>
@@ -3941,16 +3956,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E59" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C59,$N$3:$N$13,0)),0.25)</f>
@@ -3963,30 +3978,30 @@
         <v>28</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>46244</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E60" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C60,$N$3:$N$13,0)),0.25)</f>
@@ -3999,10 +4014,10 @@
         <v>28</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>46244</v>
@@ -4011,16 +4026,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E61" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C61,$N$3:$N$13,0)),0.25)</f>
@@ -4033,10 +4048,10 @@
         <v>28</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>46244</v>
@@ -4045,16 +4060,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E62" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C62,$N$3:$N$13,0)),0.25)</f>
@@ -4067,10 +4082,10 @@
         <v>28</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>46244</v>
@@ -4079,16 +4094,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E63" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C63,$N$3:$N$13,0)),0.25)</f>
@@ -4101,10 +4116,10 @@
         <v>28</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>46244</v>
@@ -4113,16 +4128,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E64" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C64,$N$3:$N$13,0)),0.25)</f>
@@ -4135,10 +4150,10 @@
         <v>28</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>46244</v>
@@ -4147,16 +4162,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E65" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C65,$N$3:$N$13,0)),0.25)</f>
@@ -4169,10 +4184,10 @@
         <v>28</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>46244</v>
@@ -4181,16 +4196,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E66" s="6" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C66,$N$3:$N$13,0)),0.25)</f>
@@ -4203,10 +4218,10 @@
         <v>28</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>46244</v>
@@ -4306,79 +4321,79 @@
         <v>14</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S1" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U1" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="V1" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="W1" s="20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Z1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" s="21" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4419,63 +4434,63 @@
         <v>3</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" s="21" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="32" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N3" s="28"/>
       <c r="O3" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P3" s="30"/>
       <c r="Q3" s="27" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R3" s="28"/>
       <c r="S3" s="29" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="T3" s="30"/>
       <c r="U3" s="27" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="V3" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="W3" s="33"/>
       <c r="Z3" s="25" t="s">
@@ -4485,133 +4500,133 @@
         <v>2</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="36" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P4" s="37"/>
       <c r="Q4" s="34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R4" s="35"/>
       <c r="S4" s="36" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="T4" s="37"/>
       <c r="U4" s="38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Z4" s="25" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AA4" s="26" t="n">
         <v>10</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="37"/>
       <c r="E5" s="38" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K5" s="36"/>
       <c r="L5" s="37"/>
       <c r="M5" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N5" s="35"/>
       <c r="O5" s="36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P5" s="37"/>
       <c r="Q5" s="34"/>
       <c r="R5" s="35"/>
       <c r="S5" s="36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="T5" s="37"/>
       <c r="U5" s="34"/>
       <c r="V5" s="35"/>
       <c r="Z5" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AA5" s="26" t="n">
         <v>4</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4620,51 +4635,51 @@
       <c r="C6" s="36"/>
       <c r="D6" s="37"/>
       <c r="E6" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K6" s="36"/>
       <c r="L6" s="37"/>
       <c r="M6" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N6" s="35"/>
       <c r="O6" s="36" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="P6" s="37"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="35"/>
       <c r="S6" s="38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="T6" s="40" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="U6" s="34"/>
       <c r="V6" s="35"/>
       <c r="Z6" s="25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA6" s="26" t="n">
         <v>6</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4673,43 +4688,43 @@
       <c r="C7" s="36"/>
       <c r="D7" s="37"/>
       <c r="E7" s="41" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="37"/>
       <c r="I7" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="35"/>
       <c r="K7" s="36"/>
       <c r="L7" s="37"/>
       <c r="M7" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N7" s="35"/>
       <c r="O7" s="36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P7" s="37"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35"/>
       <c r="S7" s="36" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="34"/>
       <c r="V7" s="35"/>
       <c r="Z7" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA7" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4719,22 +4734,22 @@
       <c r="D8" s="37"/>
       <c r="E8" s="43"/>
       <c r="F8" s="44" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="37"/>
       <c r="I8" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" s="35"/>
       <c r="K8" s="36"/>
       <c r="L8" s="37"/>
       <c r="M8" s="34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N8" s="35"/>
       <c r="O8" s="36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P8" s="37"/>
       <c r="Q8" s="34"/>
@@ -4744,13 +4759,13 @@
       <c r="U8" s="34"/>
       <c r="V8" s="35"/>
       <c r="Z8" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA8" s="26" t="n">
         <v>9</v>
       </c>
       <c r="AB8" s="25" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4759,10 +4774,10 @@
       <c r="C9" s="36"/>
       <c r="D9" s="37"/>
       <c r="E9" s="45" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="37"/>
@@ -4771,11 +4786,11 @@
       <c r="K9" s="36"/>
       <c r="L9" s="37"/>
       <c r="M9" s="34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N9" s="35"/>
       <c r="O9" s="36" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P9" s="37"/>
       <c r="Q9" s="34"/>
@@ -4785,13 +4800,13 @@
       <c r="U9" s="34"/>
       <c r="V9" s="35"/>
       <c r="Z9" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA9" s="26" t="n">
         <v>8</v>
       </c>
       <c r="AB9" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4800,10 +4815,10 @@
       <c r="C10" s="36"/>
       <c r="D10" s="37"/>
       <c r="E10" s="34" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G10" s="36"/>
       <c r="H10" s="37"/>
@@ -4812,11 +4827,11 @@
       <c r="K10" s="36"/>
       <c r="L10" s="37"/>
       <c r="M10" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N10" s="35"/>
       <c r="O10" s="36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P10" s="37"/>
       <c r="Q10" s="34"/>
@@ -4826,13 +4841,13 @@
       <c r="U10" s="34"/>
       <c r="V10" s="35"/>
       <c r="Z10" s="25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA10" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4841,10 +4856,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="37"/>
       <c r="E11" s="34" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G11" s="36"/>
       <c r="H11" s="37"/>
@@ -4853,7 +4868,7 @@
       <c r="K11" s="36"/>
       <c r="L11" s="37"/>
       <c r="M11" s="34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
@@ -4865,13 +4880,13 @@
       <c r="U11" s="34"/>
       <c r="V11" s="35"/>
       <c r="Z11" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA11" s="26" t="n">
         <v>5</v>
       </c>
       <c r="AB11" s="25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4881,7 +4896,7 @@
       <c r="D12" s="37"/>
       <c r="E12" s="43"/>
       <c r="F12" s="47" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="37"/>
@@ -4890,7 +4905,7 @@
       <c r="K12" s="36"/>
       <c r="L12" s="37"/>
       <c r="M12" s="34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
@@ -4902,13 +4917,13 @@
       <c r="U12" s="34"/>
       <c r="V12" s="35"/>
       <c r="Z12" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA12" s="26" t="n">
         <v>2</v>
       </c>
       <c r="AB12" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4917,10 +4932,10 @@
       <c r="C13" s="36"/>
       <c r="D13" s="37"/>
       <c r="E13" s="45" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G13" s="36"/>
       <c r="H13" s="37"/>
@@ -4939,13 +4954,13 @@
       <c r="U13" s="34"/>
       <c r="V13" s="35"/>
       <c r="Z13" s="48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA13" s="49" t="n">
         <v>1</v>
       </c>
       <c r="AB13" s="48" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4954,10 +4969,10 @@
       <c r="C14" s="36"/>
       <c r="D14" s="37"/>
       <c r="E14" s="34" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G14" s="36"/>
       <c r="H14" s="37"/>
@@ -4982,10 +4997,10 @@
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
       <c r="E15" s="54" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G15" s="52"/>
       <c r="H15" s="53"/>
@@ -5163,15 +5178,15 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E19" s="59" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E20" s="13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V20" s="60" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W20" s="61" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"PASS")</f>
@@ -5184,7 +5199,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V21" s="60" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="W21" s="63" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"Avoid")</f>
@@ -5197,7 +5212,7 @@
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V22" s="60" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="W22" s="65" t="n">
         <f aca="false">SUM(W20:W21)</f>

--- a/CANDIDATES LIST.xlsx
+++ b/CANDIDATES LIST.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Screen_Candidates" sheetId="1" state="visible" r:id="rId3"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="286">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -298,6 +298,9 @@
     <t xml:space="preserve">Medical Instruments &amp; Supplies</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: decisive floor failure (~2.00 quant-only) -- Rule 3 auto-Avoid: FCF yield 1.7% and contracting (2), revenue growth CAGR 3.8% (2), FCF margin 1.8% and contracting (2). Also valuation 2 (P/FCF 59x, 275% of 5-yr avg), analyst consensus 1 (15% buy), ROIC -1.2% vs 6.0% WACC. No Fidelity scan warranted. See Journal row 79.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Real Estate</t>
   </si>
   <si>
@@ -310,12 +313,18 @@
     <t xml:space="preserve">Electrical Equipment &amp; Parts</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: floor failure (~2.78 quant-only, below the 3.0 floor) -- FCF yield -0.1% (3, expanding), revenue CAGR 19.1% but CV 0.63 (3), FCF margin -4.1% (2, expanding), ROIC -1.8% vs 14.8% WACC. The strong tape (RS +139.8% vs SPY, trend 5) is an AI-datacenter-power momentum story, not a fundamentals pass. Revisit only if FCF turns solidly positive. No Fidelity scan warranted. See Journal row 79.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BSX</t>
   </si>
   <si>
     <t xml:space="preserve">Boston Scientific Corporation</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~4.33 quant-only (fcf_yield 4 [5.0%], revenue growth 5 [CAGR 16.5%, CV 0.19], FCF margin 4 [15.5% and expanding], valuation 5 [PEG 0.63]; max correlation only +0.33 vs NFLX). But relative_strength=1 (-59.6% blended vs SPY) AND technical_trend=1 (below 200-wk MA, MACD and Supertrend bearish) both sit at the floor -- Rule 5 review required. Fidelity scan + web check done: unlike INTU, the weakness has a concrete fundamental cause, not sentiment alone -- U.S. electrophysiology growth stalled (+3% in Q2 vs +23% intl; Medtronic Sphere-9 taking share; U.S. already ~80% PFA), Watchman stand-alone procedures fell low-teens on new clinical evidence, FY26 organic growth guide cut to 5-6% with 'limited adjusted EPS growth in 2027', and an 8/25/26 cyber incident disrupted manufacturing and order shipping, after which Q3/FY26 guidance was reportedly pulled (hit unquantified; 8-Ks not yet read). Offsetting: Equity Summary Score Bullish 7.5/10 (3 Buy/3 Neutral/1 Underperform/1 Sell), P/E 17.5 vs industry 39.8 (own 5-yr avg 64.9), TTM EPS +47% vs industry +10.5%, four straight EPS beats, short interest only 3.2%. Revenue Visibility can't be scored sensibly while guidance is withdrawn -- held at Watch until Q3 earnings 10/28/26 (confirmed), then fresh draft + judgment indicators with evidence. See Journal row 78, Open Items #21.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Utilities</t>
   </si>
   <si>
@@ -325,6 +334,9 @@
     <t xml:space="preserve">Cerebras Systems Inc.</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~3.11 quant-only, marginal -- revenue CAGR 174.6% (4, CV 0.44) and 100% buy sell-side, but FCF margin -86.8% (2, expanding) and FCF yield -1.1% (3). No price data in the pipeline at all (apparently a recent listing), so technical_trend / relative_strength / ROIC-vs-WACC / correlation could not be drafted and Rule 5 can't be evaluated. Fidelity overview: $166.43, 52-week range $160.81-$386.34 (-57% from the high), no Equity Summary Score. Technology is also over its sector cap (headroom -0.9%). Rejected rather than scored further; could be re-screened after ~52 weeks of trading history and a path to positive FCF. See Journal row 79. (Earlier note: FCF turned negative vs. prior FY -- % growth figure reflects a swing off a positive base.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCI</t>
   </si>
   <si>
@@ -382,6 +394,9 @@
     <t xml:space="preserve">REIT - Industrial</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: decisive floor failure (1.00 quant-only) -- all three quant Tier 1 indicators at 1: FCF yield -6.2% and contracting, revenue CAGR -3.7%, FCF margin -9.5% and contracting (Rules 2 and 3). Caveat: it's a REIT and this pipeline has no AFFO-based adaptation (development capex depresses FCF), but shrinking revenue fails regardless. ROIC 0.1% vs 5.6% WACC. No Fidelity scan warranted. See Journal row 79. (Earlier note: FCF turned negative vs. prior FY -- % growth figure reflects a swing off a positive base.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRK</t>
   </si>
   <si>
@@ -502,6 +517,9 @@
     <t xml:space="preserve">Diagnostics &amp; Research</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~3.89 quant-only, but only on the strength of a 6.1% FCF yield (5, expanding) -- growth is stagnant (revenue CAGR 2.1%, CV 0.64 -&gt; 3), FCF margin 9.2% (3), valuation 3, ROIC 3.3% vs 9.5% WACC (1), relative_strength 3 (-3.6% vs SPY). Fidelity scan: Equity Summary Score Bullish 8.3 (2 positive/3 neutral/0 bearish) and forward P/E 16 vs industry 54.5, but GAAP EPS collapsed (TTM -94%, last quarter -63%; Q4'25 missed by $0.60), 1-yr -15.8% vs industry +36.3%, UBS cut to Neutral 9/30. Price fell ~60% Jan-Feb 2026 ($203 -&gt; $80 close low) and has since retraced to $162. Alan's call: too weak to take further -- rejected to clear the list. Q3 earnings 10/20/26 (unconfirmed). See Journal row 79.</t>
+  </si>
+  <si>
     <t xml:space="preserve">INTU</t>
   </si>
   <si>
@@ -547,7 +565,7 @@
     <t xml:space="preserve">Mirion Technologies, Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prior-year FCF base is very small in dollar terms -- the % growth figure isn't a meaningful growth rate on its own; look at the dollar trend instead.</t>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~3.44 quant-only (thin -- fcf_yield 4, revenue growth 3 [CAGR 8.8%], FCF margin 3 [9.9%]) with relative_strength=1 (-47.0% blended vs SPY, Rule 5 trigger) AND roic_vs_wacc=1 (2.5% vs 9.7% WACC). Fidelity scan confirms rather than contradicts the weak price: independent-firm Equity Summary Score Bearish 1.4-1.6/10 (3 Neutral/2 Sell) despite 91% sell-side buy-equivalent; TTM EPS only $0.10 (P/E ~144-156 vs industry 45), last-quarter EPS growth 0.00% vs industry +86.5%; price -38% over 52 weeks vs industry +63%; short interest 16.9% and rising (10.9 days to cover). Growth is acquisition-led (2026 revenue guide ~22-24% includes FX and M&amp;A) with ~$20M net insider selling over the past year. Rejected rather than scored further. See Journal row 78. (Earlier note: prior-year FCF base is very small in dollar terms -- the % growth figure isn't a meaningful growth rate on its own; look at the dollar trend instead.)</t>
   </si>
   <si>
     <t xml:space="preserve">MRVL</t>
@@ -616,6 +634,9 @@
     <t xml:space="preserve">Natera, Inc.</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~3.44 quant-only (revenue growth 5 [CAGR 41.1%, CV 0.26], FCF yield 3 [-0.5% but expanding], FCF margin 2 [-12.1%, expanding]); relative_strength 5 (+104% vs SPY), trend 5, volume 5; ROIC -24.1% vs 11.2% WACC (1); max correlation +0.42 vs CRWD. Clears the floor with no Rule 5 trigger, but Fidelity shows the INTU pattern: independent-firm Equity Summary Score Bearish 1.5 (ISS-EVA Underperform, Verus and Jefferson Sell, Zacks/McLean Neutral, Trading Central Buy) against a 91% buy sell-side. Stock +154% in a year at 94% of its 52-week range; normalized FCF negative after SBC (-$278M), GAAP EPS -$1.35 (no P/FCF or P/E anchor), EPS results erratic (2 misses, 2 beats in the last 4). Growth and improving FCF are real. Held at Watch until Q3 earnings 11/4/26 (unconfirmed) -- look for normalized FCF turning positive. See Journal row 79, Open Items #23.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OKE</t>
   </si>
   <si>
@@ -667,6 +688,9 @@
     <t xml:space="preserve">Industrial Distribution</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: floor failure (~2.44 quant-only) -- Rule 3 auto-Avoid: FCF margin 0.6% (2) and revenue growth consistency 2, though that one is an artifact of a transformational acquisition (revenue $57M -&gt; $6.8B in one year, CAGR 434%), so there is no clean growth history either way. FCF yield 0.3%. relative_strength=1 (-54.8% vs SPY) AND technical_trend=1 (Rule 5 as well), ROIC -1.2% vs 8.3% WACC. 100% buy sell-side doesn't change the read. No Fidelity scan warranted. See Journal row 79. (Earlier note: prior-year FCF base is very small in dollar terms -- the % growth figure isn't a meaningful growth rate on its own; look at the dollar trend instead.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLB</t>
   </si>
   <si>
@@ -682,6 +706,9 @@
     <t xml:space="preserve">NuScale Power Corporation</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: decisive floor failure (~1.56 quant-only) -- Rule 3 auto-Avoid: pre-revenue economics (FCF margin -1,522%, FCF yield -15.1%), revenue growth consistency 2 (CV 0.97). relative_strength=1 (-68.2% vs SPY) AND technical_trend=1, ROIC -206% vs 20% WACC. No Fidelity scan warranted. See Journal row 79. (Earlier note: FCF losses deepened substantially year over year in real dollar terms -- genuine deterioration.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPOT</t>
   </si>
   <si>
@@ -703,6 +730,9 @@
     <t xml:space="preserve">Rental &amp; Leasing Services</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~3.11 quant-only, marginal against the 3.0 floor -- revenue growth consistency 2 (CAGR 4.9%, CV 1.08: $9.67B FY23 -&gt; $10.86B -&gt; $10.79B -&gt; $11.15B, i.e. flat for two years), fcf_yield 4 (4.8%), FCF margin 3 (13.5%), valuation 4. Rule 5 could not be evaluated: NYSE-listed only since 3/2/26 (~150 price rows), so technical_trend / relative_strength / ROIC-vs-WACC have no usable history. Fidelity scan: no Equity Summary Score or sell-side coverage at all (McLean/Zacks Neutral, Verus Sell), P/E 22.6 vs industry 23.5 (fair, not cheap), last-quarter EPS growth +19.9% vs industry +19.5% (in line), dividend $0.30/qtr (~1.6%), short interest 2.1%. Nothing lifts it above marginal; rejected rather than scored further. Could be re-screened once ~52 weeks of U.S. price history exist (~Mar 2027) or via the AHT.L UK listing (GBP -- FX distorts relative strength). See Journal row 78.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SWK</t>
   </si>
   <si>
@@ -712,12 +742,21 @@
     <t xml:space="preserve">Tools &amp; Accessories</t>
   </si>
   <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: floor failure (~2.56 quant-only) -- revenue shrinking (-3.7% CAGR, score 1, Rule 2) plus FCF margin 3.9% (2) = Rule 3 auto-Avoid. FCF yield 4.3% and expanding (4), trend 5 and RS +12.2% don't offset. ROIC 6.1% vs 10.0% WACC, analyst consensus 2 (27% buy). No Fidelity scan warranted. See Journal row 79.</t>
+  </si>
+  <si>
     <t xml:space="preserve">UBER</t>
   </si>
   <si>
     <t xml:space="preserve">Uber Technologies, Inc.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ground Transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial quant Tier 1 screen 10/2/26: ~4.33 quant-only (revenue growth 5 [CAGR 17.7%, CV 0.03], FCF margin 4 [15.3%, expanding], FCF yield 4 [5.7%], valuation 4 [P/FCF 41% of 5-yr avg], ROIC 3 [14.5% vs 10.4% WACC]; max correlation +0.48 vs SPMO). But relative_strength=1 (-33.9% blended vs SPY; 12mo -45.1%) triggers Rule 5. Fidelity scan: Equity Summary Score Neutral 3.9 (6 Neutral/1 Sell/1 Buy -- not decisively bearish), P/E 14.9 vs industry 21.7, forward 20.7 vs 21.7, 1-yr -29.7% vs industry +10.5%, near its 52-week low; the narrative risk is robotaxi/AV disruption (new California robotaxi law 10/2) and driver-wage litigation (Lyft's $272.5M California settlement 10/1). Last-quarter EPS growth +85.7% vs industry +37.5% (GAAP, noisy: two of the last four quarters missed). SECTOR: Alan ruled 10/2/26 that UBER counts as Industrials (Fidelity/GICS: Ground Transportation), not the Technology yfinance assigns -- Sector/Industry corrected here, headroom now +23.8%; if scored, set the Scoring tab's sector by hand. Held at Watch until Q3 earnings 11/2/26 (unconfirmed). See Journal row 79, Open Items #22.</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNH</t>
   </si>
   <si>
@@ -727,9 +766,6 @@
     <t xml:space="preserve">Healthcare Plans</t>
   </si>
   <si>
-    <t xml:space="preserve">PENDING</t>
-  </si>
-  <si>
     <t xml:space="preserve">Watch - Pending Litigation</t>
   </si>
   <si>
@@ -758,6 +794,10 @@
   </si>
   <si>
     <t xml:space="preserve">Health Information Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FULL TIER 1-3 SCORED 10/2/26: Composite 81.6, STRONG BUY (Scoring row 51) -- Moat 4/M, Revenue Visibility 5/M, Management 4/M, judgment approved by Alan. He leans conservative on Moat (3 would give 78.6, BUY) and approved 4 on the basis of re-evaluating at the purchase decision; STRONG BUY needs both Moat 4 and Visibility 5 (any single downgrade -&gt; BUY). See Journal row 80, Open Items #24.
+Screen detail: Initial quant Tier 1 screen 10/2/26: ~4.22 quant-only (fcf_yield 4 [2.1%, expanding], revenue growth 4 [CAGR 14.0%, CV 0.22], FCF margin 5 [29.5%, expanding], valuation 4 [P/FCF 67% of 5-yr avg]); no Rule 5 trigger (trend 5, relative_strength 4 [+12.4%]); ROIC 11.8% vs 10.8% WACC (2); max correlation +0.51 vs ADBE (software-factor overlap although it buckets as Healthcare). FCF uses a derived capex of zero -- VEEV's statement has no capex row (tool gap found and fixed this session, see CLAUDE.md), so FCF may be slightly overstated. Fidelity scan: Equity Summary Score Bullish 8.2 (3 positive/4 neutral/0 bearish), TTM EPS growth +24.9% vs industry +17.7%, four straight beats, P/E 46 vs own 5-yr avg 61, forward P/E 30.5 (CRM 14, MSFT 26), short interest 3.4%; fell 51% Oct '25-Apr '26 and has rebounded 80%. Cleared for full Part 12 research (Moat/Revenue Visibility/Management) -- Alan OK'd 10/2/26. Q3 earnings 11/18/26 (unconfirmed). See Journal row 79.</t>
   </si>
   <si>
     <t xml:space="preserve">VFC</t>
@@ -851,7 +891,7 @@
     <t xml:space="preserve">ABT, AZN, BAX, BSX, ICLR, NTRA, PFE, UNH, VEEV, XRAY</t>
   </si>
   <si>
-    <t xml:space="preserve">BE, GXO, MIR, QXO, SMR, SUNB, SWK, UPS</t>
+    <t xml:space="preserve">BE, GXO, MIR, QXO, SMR, SUNB, SWK, UBER, UPS</t>
   </si>
   <si>
     <t xml:space="preserve"> VFC</t>
@@ -866,7 +906,7 @@
     <t xml:space="preserve"> GOOS</t>
   </si>
   <si>
-    <t xml:space="preserve">ACN, CBRS, INTU, NOW, UBER</t>
+    <t xml:space="preserve">ACN, CBRS, INTU, NOW</t>
   </si>
   <si>
     <t xml:space="preserve">Divers. retail/e-commerce</t>
@@ -1280,7 +1320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1290,6 +1330,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1297,7 +1341,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1333,15 +1377,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1365,7 +1409,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1573,7 +1617,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2028,2348 +2072,2364 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="2" min="2" style="0" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="2" min="2" style="2" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="3" min="3" style="1" width="19.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="4" min="4" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="14.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C2,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="10" t="n">
         <v>-2.10416666666667</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C3,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="10" t="n">
         <v>0.164383561643836</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="15" t="n">
+      <c r="O3" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C4,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>0.26232947682041</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J4" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="15" t="n">
+      <c r="O4" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C5,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>0.149703138252757</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="15" t="n">
+      <c r="O5" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C6,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>1.75074928488446</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="15" t="n">
+      <c r="O6" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C7,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>1.03698878704695</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="15" t="n">
+      <c r="O7" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C8,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>0.901546112822155</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="15" t="n">
+      <c r="O8" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C9,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>0.191752577319588</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="17" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="15" t="n">
+      <c r="O9" s="16" t="n">
         <v>0.0342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C10,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>-1.65419090240788</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="O10" s="15" t="n">
+      <c r="O10" s="16" t="n">
         <v>0.0119</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C11,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>-0.422182468694097</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="11" t="n">
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="N11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="O11" s="15" t="n">
+      <c r="N11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" s="16" t="n">
         <v>0.0249</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="6" t="s">
+    <row r="12" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="8" t="n">
+      <c r="D12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C12,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.725396729620467</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="11" t="n">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="N12" s="14" t="s">
+      <c r="K12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="15" t="n">
+      <c r="O12" s="16" t="n">
         <v>0.2586</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="7" t="s">
+    <row r="13" customFormat="false" ht="333" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C13,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>0.439323467230444</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="11" t="n">
+      <c r="H13" s="8"/>
+      <c r="I13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="N13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="O13" s="15" t="n">
+      <c r="K13" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="7" t="s">
+    <row r="14" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C14,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>-1.91656846570823</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="11" t="n">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>64</v>
+      <c r="K14" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="8" t="n">
+      <c r="A15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C15,$N$3:$N$13,0)),0.25)</f>
         <v>0.2251</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.0390314419949404</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K15" s="12" t="s">
-        <v>81</v>
+      <c r="K15" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="A16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="8" t="n">
+      <c r="D16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C16,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <v>0.512241054613936</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K16" s="12"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="8" t="n">
+      <c r="D17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C17,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>-0.733898305084746</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K17" s="12"/>
+      <c r="K17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="A18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C18,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>0.512541254125413</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>90</v>
+      <c r="K18" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="A19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="8" t="n">
+      <c r="D19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C19,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>-0.0422653927658648</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="8" t="n">
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C20,$N$3:$N$13,0)),0.25)</f>
         <v>0.2251</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>-3.12073931594724</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="11" t="n">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K20" s="12" t="s">
-        <v>64</v>
+      <c r="K20" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="A21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="8" t="n">
+      <c r="D21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C21,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>0.0575678887372915</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K21" s="12"/>
+      <c r="K21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="A22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="8" t="n">
+      <c r="D22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C22,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="10" t="n">
         <v>0.189944134078212</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K22" s="12"/>
+      <c r="K22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="A23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="8" t="n">
+      <c r="D23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C23,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="10" t="n">
         <v>0.177357167893446</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K23" s="12"/>
+      <c r="K23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="A24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="8" t="n">
+      <c r="D24" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C24,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>0.311500511706757</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K24" s="12"/>
+      <c r="K24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="A25" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="8" t="n">
+      <c r="D25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C25,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>0.964179104477612</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J25" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K25" s="12"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="A26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" s="8" t="n">
+      <c r="D26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C26,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>-0.476164532824843</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J26" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K26" s="12"/>
+      <c r="K26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="A27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C27,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>-0.0990463643787969</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J27" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K27" s="12"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="84.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="A28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="8" t="n">
+      <c r="D28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C28,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>1.18235294117647</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="7" t="s">
+      <c r="H28" s="7"/>
+      <c r="I28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>119</v>
+      <c r="K28" s="13" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="A29" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="8" t="n">
+      <c r="D29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C29,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>-0.483941605839416</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J29" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K29" s="12"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="A30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" s="8" t="n">
+      <c r="D30" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C30,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="10" t="n">
         <v>-0.421052631578947</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J30" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>126</v>
+      <c r="K30" s="13" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="7" t="s">
+      <c r="A31" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E31" s="8" t="n">
+      <c r="D31" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C31,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>-0.471097113027159</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K31" s="12"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="A32" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" s="8" t="n">
+      <c r="D32" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C32,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="10" t="n">
         <v>0.464687819856704</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="7" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="J32" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" s="7" t="s">
+      <c r="K32" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="8" t="n">
+      <c r="D33" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C33,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="10" t="n">
         <v>-0.229396419784872</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J33" s="11" t="n">
+      <c r="H33" s="8"/>
+      <c r="I33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K33" s="12"/>
+      <c r="K33" s="13" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="A34" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="8" t="n">
+      <c r="D34" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C34,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>0.312688821752266</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="18" t="s">
+      <c r="H34" s="8"/>
+      <c r="I34" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J34" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K34" s="12" t="s">
-        <v>140</v>
+      <c r="K34" s="13" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="7" t="s">
+      <c r="A35" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" s="8" t="n">
+      <c r="D35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C35,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>32.6945032891069</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7" t="s">
+      <c r="H35" s="7"/>
+      <c r="I35" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>144</v>
+      <c r="K35" s="13" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="7" t="s">
+      <c r="A36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="8" t="n">
+      <c r="D36" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C36,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>-0.920909498710329</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="11" t="n">
+      <c r="J36" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K36" s="12"/>
+      <c r="K36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C37" s="7" t="s">
+      <c r="A37" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="8" t="n">
+      <c r="D37" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C37,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="10" t="n">
         <v>0.0330897279740154</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J37" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K37" s="12"/>
-    </row>
-    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="K37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="8" t="n">
+      <c r="D38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C38,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>1.12524850894632</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J38" s="11" t="n">
+      <c r="H38" s="8"/>
+      <c r="I38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K38" s="12" t="s">
-        <v>152</v>
+      <c r="K38" s="13" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C39" s="7" t="s">
+      <c r="A39" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C39,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>0.00165515256188831</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7" t="s">
+      <c r="H39" s="7"/>
+      <c r="I39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J39" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K39" s="12" t="s">
-        <v>155</v>
+      <c r="K39" s="13" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="7" t="s">
+      <c r="A40" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" s="8" t="n">
+      <c r="D40" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C40,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="10" t="n">
         <v>0.343682699210337</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="7" t="s">
+      <c r="H40" s="7"/>
+      <c r="I40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J40" s="12" t="n">
         <v>46264</v>
       </c>
-      <c r="K40" s="12" t="s">
-        <v>159</v>
+      <c r="K40" s="13" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C41" s="7" t="s">
+      <c r="A41" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D41" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C41,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>0.366843517880975</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="J41" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K41" s="12" t="s">
-        <v>162</v>
+      <c r="K41" s="13" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C42" s="7" t="s">
+      <c r="A42" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E42" s="8" t="n">
+      <c r="D42" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E42" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C42,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>-0.331701346389229</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="J42" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K42" s="12"/>
+      <c r="K42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="A43" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" s="8" t="n">
+      <c r="D43" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C43,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>-0.080797481636936</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K43" s="12"/>
+      <c r="K43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="A44" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" s="8" t="n">
+      <c r="D44" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C44,$N$3:$N$13,0)),0.25)</f>
         <v>-0.0086</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>0.343111111111111</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="J44" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K44" s="12"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E45" s="8" t="n">
+      <c r="A45" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C45,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>-0.578744493392071</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J45" s="11" t="n">
+      <c r="J45" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K45" s="12"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C46" s="7" t="s">
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="217.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="8" t="n">
+      <c r="D46" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C46,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>0.295628638545603</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J46" s="11" t="n">
+      <c r="H46" s="8"/>
+      <c r="I46" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K46" s="12"/>
+      <c r="K46" s="13" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C47" s="7" t="s">
+      <c r="A47" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" s="8" t="n">
+      <c r="D47" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C47,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>-0.146494593651901</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
+      <c r="H47" s="8"/>
+      <c r="I47" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="J47" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K47" s="12" t="s">
-        <v>177</v>
+      <c r="K47" s="13" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" s="7" t="s">
+      <c r="A48" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E48" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C48,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="10" t="n">
         <v>-0.0772750381291307</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I48" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J48" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K48" s="12" t="s">
-        <v>180</v>
+      <c r="K48" s="13" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C49" s="7" t="s">
+      <c r="A49" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49" s="8" t="n">
+      <c r="D49" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E49" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C49,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="10" t="n">
         <v>0.078538877812589</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J49" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K49" s="12"/>
+      <c r="K49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C50" s="7" t="s">
+      <c r="A50" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="8" t="n">
+      <c r="D50" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E50" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C50,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="10" t="n">
         <v>-0.177774493867297</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I50" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J50" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K50" s="12" t="s">
-        <v>186</v>
+      <c r="K50" s="13" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C51" s="7" t="s">
+      <c r="A51" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E51" s="8" t="n">
+      <c r="D51" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C51,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>0.510044512123697</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="7" t="s">
+      <c r="H51" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J51" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K51" s="12"/>
-    </row>
-    <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C52" s="7" t="s">
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E52" s="8" t="n">
+      <c r="D52" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C52,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="10" t="n">
         <v>1.1629279811098</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J52" s="11" t="n">
+      <c r="H52" s="8"/>
+      <c r="I52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K52" s="12" t="s">
-        <v>152</v>
+      <c r="K52" s="13" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53" s="7" t="s">
+      <c r="A53" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="8" t="n">
+      <c r="D53" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C53,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="10" t="n">
         <v>0.0156494522691706</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I53" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J53" s="11" t="n">
+      <c r="J53" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K53" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C54" s="7" t="s">
+      <c r="K53" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="8" t="n">
+      <c r="D54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E54" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C54,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="10" t="n">
         <v>-3.23252690644835</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J54" s="11" t="n">
+      <c r="H54" s="8"/>
+      <c r="I54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K54" s="12" t="s">
-        <v>19</v>
+      <c r="K54" s="13" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C55" s="7" t="s">
+      <c r="A55" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E55" s="8" t="n">
+      <c r="D55" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E55" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C55,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="10" t="n">
         <v>0.257443082311734</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="11" t="n">
+      <c r="J55" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K55" s="12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C56" s="7" t="s">
+      <c r="K55" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="8" t="n">
+      <c r="D56" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C56,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" s="10" t="n">
         <v>0.393139841688654</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J56" s="11" t="n">
+      <c r="H56" s="8"/>
+      <c r="I56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" s="7" t="s">
+      <c r="K56" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" s="8" t="n">
+      <c r="D57" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E57" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C57,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" s="10" t="n">
         <v>-0.0864541832669323</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J57" s="11" t="n">
+      <c r="H57" s="8"/>
+      <c r="I57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K57" s="12"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E58" s="8" t="n">
+      <c r="K57" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C58,$N$3:$N$13,0)),0.25)</f>
-        <v>-0.0086</v>
-      </c>
-      <c r="F58" s="9" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="F58" s="10" t="n">
         <v>0.415953589557651</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J58" s="11" t="n">
+      <c r="H58" s="8"/>
+      <c r="I58" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K58" s="12"/>
+      <c r="K58" s="13" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C59" s="7" t="s">
+      <c r="A59" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E59" s="8" t="n">
+      <c r="D59" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E59" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C59,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" s="10" t="n">
         <v>-0.22361748369959</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H59" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J59" s="11" t="n">
+      <c r="H59" s="8"/>
+      <c r="I59" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="J59" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K59" s="12" t="s">
-        <v>214</v>
+      <c r="K59" s="13" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C60" s="7" t="s">
+      <c r="A60" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="8" t="n">
+      <c r="D60" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C60,$N$3:$N$13,0)),0.25)</f>
         <v>0.2381</v>
       </c>
-      <c r="F60" s="9" t="n">
+      <c r="F60" s="10" t="n">
         <v>-0.233059713503943</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H60" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I60" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J60" s="11" t="n">
+      <c r="J60" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K60" s="12" t="s">
-        <v>217</v>
+      <c r="K60" s="13" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="7" t="s">
+      <c r="A61" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" s="8" t="n">
+      <c r="D61" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C61,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F61" s="9" t="n">
+      <c r="F61" s="10" t="n">
         <v>0.154282351682448</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H61" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="I61" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="11" t="n">
+      <c r="J61" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K61" s="12"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C62" s="7" t="s">
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" customFormat="false" ht="349.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="E62" s="8" t="n">
+      <c r="D62" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E62" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C62,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F62" s="10" t="n">
         <v>0.29831081298031</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J62" s="11" t="n">
+      <c r="H62" s="8"/>
+      <c r="I62" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K62" s="12"/>
+      <c r="K62" s="13" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C63" s="7" t="s">
+      <c r="A63" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E63" s="8" t="n">
+      <c r="D63" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C63,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F63" s="9" t="n">
+      <c r="F63" s="10" t="n">
         <v>0.490119777249103</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="I63" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J63" s="11" t="n">
+      <c r="J63" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K63" s="12" t="s">
-        <v>225</v>
+      <c r="K63" s="13" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" s="8" t="n">
+      <c r="A64" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C64,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F64" s="10" t="n">
         <v>-0.469617706237425</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="I64" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J64" s="11" t="n">
+      <c r="J64" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K64" s="12"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C65" s="7" t="s">
+      <c r="A65" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C65,$N$3:$N$13,0)),0.25)</f>
         <v>0.2158</v>
       </c>
-      <c r="F65" s="9" t="n">
+      <c r="F65" s="10" t="n">
         <v>-0.629893238434164</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I65" s="7" t="s">
+      <c r="I65" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J65" s="11" t="n">
+      <c r="J65" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K65" s="12" t="s">
-        <v>230</v>
+      <c r="K65" s="13" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C66" s="7" t="s">
+      <c r="A66" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E66" s="8" t="n">
+      <c r="D66" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E66" s="9" t="n">
         <f aca="false">IFERROR(0.25-INDEX($O$3:$O$13,MATCH(C66,$N$3:$N$13,0)),0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F66" s="9" t="n">
+      <c r="F66" s="10" t="n">
         <v>0.144553072625698</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I66" s="7" t="s">
+      <c r="I66" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J66" s="11" t="n">
+      <c r="J66" s="12" t="n">
         <v>46244</v>
       </c>
-      <c r="K66" s="12"/>
+      <c r="K66" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K66">
@@ -4434,1025 +4494,1047 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultColWidth="10.8359375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="14.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="19" width="6.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="19" width="8.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="19" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="19" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="19" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="19" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="19" width="7.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="19" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="20" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="21" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="21" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="6.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="20" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="20" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="20" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="20" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="20" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="21" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="22" width="5.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="22" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="28.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="8.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="47.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="29" style="21" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="2" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="2" width="47.85"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="29" style="22" width="10.82"/>
   </cols>
   <sheetData>
-    <row r="1" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+    <row r="1" s="28" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="I1" s="22" t="s">
+      <c r="D1" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="K1" s="24" t="s">
+      <c r="J1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="K1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="M1" s="22" t="s">
+      <c r="L1" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="M1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="O1" s="24" t="s">
+      <c r="N1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="O1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q1" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="S1" s="24" t="s">
+      <c r="P1" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q1" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="S1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="V1" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="W1" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z1" s="28" t="s">
+      <c r="T1" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="U1" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB1" s="28" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" s="27" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="29" t="n">
+      <c r="AA1" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB1" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" s="28" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="30" t="n">
         <f aca="false">SUM(A16,C16,E16,G16,I16,K16,M16,O16,Q16,S16,U16)</f>
         <v>55</v>
       </c>
-      <c r="X2" s="30" t="n">
+      <c r="X2" s="31" t="n">
         <f aca="false">W2/W2</f>
         <v>1</v>
       </c>
-      <c r="Z2" s="31" t="s">
+      <c r="Z2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="AA2" s="32" t="n">
+      <c r="AA2" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="AB2" s="33" t="s">
+      <c r="AB2" s="34" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" s="28" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="39"/>
+      <c r="F3" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="44"/>
+      <c r="U3" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="V3" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="45"/>
+      <c r="Z3" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="34" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L4" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="55"/>
+      <c r="O4" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="P4" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="50" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="35" t="s">
+      <c r="V4" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z4" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA4" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="37" t="s">
+      <c r="I5" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="35" t="s">
+      <c r="O5" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="P5" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="L3" s="37" t="s">
+      <c r="Q5" s="46"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="T5" s="57"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="47"/>
+      <c r="Z5" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA5" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB5" s="34" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="41" t="s">
+      <c r="G6" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="I6" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="52"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" s="55"/>
+      <c r="O6" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="P6" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="T6" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="U6" s="46"/>
+      <c r="V6" s="47"/>
+      <c r="Z6" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA6" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="58" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="52"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="52"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="N7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="47"/>
+      <c r="Z7" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA7" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="52"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="52"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="N8" s="55"/>
+      <c r="O8" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="P8" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="47"/>
+      <c r="Z8" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA8" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="N9" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="47"/>
+      <c r="Z9" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA9" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="34" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="46"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" s="52"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="N10" s="55"/>
+      <c r="O10" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="47"/>
+      <c r="Z10" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="34" t="s">
+      <c r="AA10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="34" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="46"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="52"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="50" t="s">
+        <v>232</v>
+      </c>
+      <c r="N11" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="P11" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="47"/>
+      <c r="Z11" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA11" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="34" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="46"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="G12" s="52"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" s="52"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="47"/>
+      <c r="Z12" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="AA12" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" s="34" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="46"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="43"/>
-      <c r="U3" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="V3" s="35" t="s">
+      <c r="G13" s="52"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="47"/>
+      <c r="Z13" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA13" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="67" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="46"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="44"/>
-      <c r="Z3" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA3" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" s="33" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="48" t="s">
+      <c r="G14" s="52"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="47"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="68"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="F15" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="49" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="P4" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="R4" s="46"/>
-      <c r="S4" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="T4" s="55"/>
-      <c r="U4" s="49" t="s">
-        <v>226</v>
-      </c>
-      <c r="V4" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z4" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA4" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB4" s="33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>244</v>
-      </c>
-      <c r="F5" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="51"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" s="46"/>
-      <c r="O5" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="T5" s="56"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="46"/>
-      <c r="Z5" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA5" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" s="33" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="H6" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="J6" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="51"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6" s="46"/>
-      <c r="O6" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="T6" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="U6" s="45"/>
-      <c r="V6" s="46"/>
-      <c r="Z6" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA6" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" s="33" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="57" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="51"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="J7" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="51"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="T7" s="55"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="46"/>
-      <c r="Z7" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA7" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" s="33" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="G8" s="51"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="J8" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="51"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="N8" s="46"/>
-      <c r="O8" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="46"/>
-      <c r="Z8" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA8" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB8" s="33" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="51"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="N9" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="46"/>
-      <c r="Z9" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA9" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="33" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>255</v>
-      </c>
-      <c r="G10" s="51"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" s="54"/>
-      <c r="O10" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="P10" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="46"/>
-      <c r="Z10" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA10" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB10" s="33" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="F11" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="51"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="46"/>
-      <c r="Z11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA11" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB11" s="33" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="63" t="s">
-        <v>259</v>
-      </c>
-      <c r="G12" s="51"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="O12" s="51"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="46"/>
-      <c r="Z12" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA12" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB12" s="33" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="51"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="45"/>
-      <c r="V13" s="46"/>
-      <c r="Z13" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="AA13" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="66" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="51"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="46"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="67"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="71" t="s">
-        <v>264</v>
-      </c>
-      <c r="F15" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="68"/>
-    </row>
-    <row r="16" s="73" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="n">
+      <c r="G15" s="70"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="69"/>
+    </row>
+    <row r="16" s="74" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
         <f aca="false">COUNTA(A3:A15)</f>
         <v>3</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="21" t="n">
         <f aca="false">COUNTA(C3:C15)</f>
         <v>3</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">COUNTA(E3:E15)</f>
         <v>10</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="21" t="n">
         <f aca="false">COUNTA(G3:G15)</f>
         <v>4</v>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="I16" s="21" t="n">
         <f aca="false">COUNTA(I3:I15)</f>
         <v>6</v>
       </c>
-      <c r="K16" s="20" t="n">
+      <c r="K16" s="21" t="n">
         <f aca="false">COUNTA(K3:K15)</f>
         <v>2</v>
       </c>
-      <c r="M16" s="20" t="n">
+      <c r="M16" s="21" t="n">
         <f aca="false">COUNTA(M3:M15)</f>
         <v>10</v>
       </c>
-      <c r="O16" s="20" t="n">
+      <c r="O16" s="21" t="n">
         <f aca="false">COUNTA(O3:O15)</f>
-        <v>8</v>
-      </c>
-      <c r="Q16" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="21" t="n">
         <f aca="false">COUNTA(Q3:Q15)</f>
         <v>2</v>
       </c>
-      <c r="S16" s="20" t="n">
+      <c r="S16" s="21" t="n">
         <f aca="false">COUNTA(S3:S15)</f>
-        <v>5</v>
-      </c>
-      <c r="U16" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" s="21" t="n">
         <f aca="false">COUNTA(U3:U15)</f>
         <v>2</v>
       </c>
-      <c r="Z16" s="20"/>
+      <c r="Z16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" s="75" t="n">
+      <c r="A17" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="76" t="n">
         <f aca="false">COUNTA(B3:B15)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="75" t="n">
+      <c r="D17" s="76" t="n">
         <f aca="false">COUNTA(D3:D15)</f>
         <v>3</v>
       </c>
-      <c r="F17" s="75" t="n">
+      <c r="F17" s="76" t="n">
         <f aca="false">COUNTA(F4:F7,F9:F11,F13:F15)</f>
         <v>10</v>
       </c>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75" t="n">
+      <c r="G17" s="76"/>
+      <c r="H17" s="76" t="n">
         <f aca="false">COUNTA(H3:H15)</f>
         <v>4</v>
       </c>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75" t="n">
+      <c r="I17" s="76"/>
+      <c r="J17" s="76" t="n">
         <f aca="false">COUNTA(J3:J15)</f>
         <v>6</v>
       </c>
-      <c r="K17" s="75"/>
-      <c r="L17" s="75" t="n">
+      <c r="K17" s="76"/>
+      <c r="L17" s="76" t="n">
         <f aca="false">COUNTA(L3:L15)</f>
         <v>2</v>
       </c>
-      <c r="M17" s="75"/>
-      <c r="N17" s="75" t="n">
+      <c r="M17" s="76"/>
+      <c r="N17" s="76" t="n">
         <f aca="false">COUNTA(N3:N15)</f>
-        <v>3</v>
-      </c>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76" t="n">
         <f aca="false">COUNTA(P3:P15)</f>
+        <v>8</v>
+      </c>
+      <c r="Q17" s="76"/>
+      <c r="R17" s="76" t="n">
+        <f aca="false">COUNTA(R3:R15)</f>
         <v>2</v>
       </c>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75" t="n">
-        <f aca="false">COUNTA(R3:R15)</f>
-        <v>1</v>
-      </c>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75" t="n">
+      <c r="S17" s="76"/>
+      <c r="T17" s="76" t="n">
         <f aca="false">COUNTA(T3:T15)</f>
-        <v>1</v>
-      </c>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="76"/>
+      <c r="V17" s="76" t="n">
         <f aca="false">COUNTA(V3:V15)</f>
         <v>2</v>
       </c>
-      <c r="W17" s="29" t="n">
+      <c r="W17" s="30" t="n">
         <f aca="false">SUM(B17,D17,F17,H17,J17,L17,N17,P17,R17,T17,V17)</f>
-        <v>37</v>
-      </c>
-      <c r="X17" s="30" t="n">
+        <v>48</v>
+      </c>
+      <c r="X17" s="31" t="n">
         <f aca="false">W17/W2</f>
-        <v>0.672727272727273</v>
+        <v>0.872727272727273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="75"/>
-      <c r="B18" s="76" t="n">
+      <c r="A18" s="76"/>
+      <c r="B18" s="77" t="n">
         <f aca="false">B17/A16</f>
         <v>1</v>
       </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="76" t="n">
+      <c r="C18" s="76"/>
+      <c r="D18" s="77" t="n">
         <f aca="false">D17/C16</f>
         <v>1</v>
       </c>
-      <c r="E18" s="75"/>
-      <c r="F18" s="76" t="n">
+      <c r="E18" s="76"/>
+      <c r="F18" s="77" t="n">
         <f aca="false">F17/E16</f>
         <v>1</v>
       </c>
-      <c r="H18" s="76" t="n">
+      <c r="H18" s="77" t="n">
         <f aca="false">H17/G16</f>
         <v>1</v>
       </c>
-      <c r="J18" s="76" t="n">
+      <c r="J18" s="77" t="n">
         <f aca="false">J17/I16</f>
         <v>1</v>
       </c>
-      <c r="L18" s="76" t="n">
+      <c r="L18" s="77" t="n">
         <f aca="false">L17/K16</f>
         <v>1</v>
       </c>
-      <c r="N18" s="76" t="n">
+      <c r="N18" s="77" t="n">
         <f aca="false">N17/M16</f>
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P18" s="77" t="n">
         <f aca="false">P17/O16</f>
-        <v>0.25</v>
-      </c>
-      <c r="R18" s="76" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="R18" s="77" t="n">
         <f aca="false">R17/Q16</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="77" t="n">
+        <f aca="false">T17/S16</f>
         <v>0.5</v>
       </c>
-      <c r="T18" s="76" t="n">
-        <f aca="false">T17/S16</f>
-        <v>0.2</v>
-      </c>
-      <c r="V18" s="76" t="n">
+      <c r="V18" s="77" t="n">
         <f aca="false">V17/U16</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77" t="s">
-        <v>266</v>
-      </c>
-      <c r="B19" s="19" t="n">
+      <c r="A19" s="78" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" s="20" t="n">
         <f aca="false">A16-B17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="20" t="n">
         <f aca="false">C16-D17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="20" t="n">
         <f aca="false">E16-F17</f>
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="20" t="n">
         <f aca="false">G16-H17</f>
         <v>0</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="20" t="n">
         <f aca="false">I16-J17</f>
         <v>0</v>
       </c>
-      <c r="L19" s="19" t="n">
+      <c r="L19" s="20" t="n">
         <f aca="false">K16-L17</f>
         <v>0</v>
       </c>
-      <c r="N19" s="19" t="n">
+      <c r="N19" s="20" t="n">
         <f aca="false">M16-N17</f>
+        <v>4</v>
+      </c>
+      <c r="P19" s="20" t="n">
+        <f aca="false">O16-P17</f>
+        <v>1</v>
+      </c>
+      <c r="R19" s="20" t="n">
+        <f aca="false">Q16-R17</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="20" t="n">
+        <f aca="false">S16-T17</f>
+        <v>2</v>
+      </c>
+      <c r="W19" s="30" t="n">
+        <f aca="false">SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19,V19)</f>
         <v>7</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">O16-P17</f>
-        <v>6</v>
-      </c>
-      <c r="R19" s="19" t="n">
-        <f aca="false">Q16-R17</f>
-        <v>1</v>
-      </c>
-      <c r="T19" s="19" t="n">
-        <f aca="false">S16-T17</f>
-        <v>4</v>
-      </c>
-      <c r="W19" s="29" t="n">
-        <f aca="false">SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19,V19)</f>
-        <v>18</v>
-      </c>
-      <c r="X19" s="78" t="n">
+      <c r="X19" s="79" t="n">
         <f aca="false">W19/W2</f>
-        <v>0.327272727272727</v>
+        <v>0.127272727272727</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E20" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="V20" s="79" t="s">
-        <v>268</v>
-      </c>
-      <c r="W20" s="80" t="n">
+      <c r="E20" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="V20" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="W20" s="81" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"PASS")</f>
-        <v>14</v>
-      </c>
-      <c r="X20" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="X20" s="82" t="n">
         <f aca="false">W20/W2</f>
-        <v>0.254545454545455</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83" t="s">
-        <v>269</v>
-      </c>
-      <c r="V21" s="79" t="s">
-        <v>270</v>
-      </c>
-      <c r="W21" s="84" t="n">
+      <c r="A21" s="83"/>
+      <c r="B21" s="84" t="s">
+        <v>282</v>
+      </c>
+      <c r="V21" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="W21" s="85" t="n">
         <f aca="false">COUNTIF($A$1:$V$15,"Avoid")</f>
-        <v>22</v>
-      </c>
-      <c r="X21" s="85" t="n">
+        <v>32</v>
+      </c>
+      <c r="X21" s="86" t="n">
         <f aca="false">W21/W2</f>
-        <v>0.4</v>
+        <v>0.581818181818182</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="V22" s="79" t="s">
-        <v>271</v>
-      </c>
-      <c r="W22" s="86" t="n">
+      <c r="V22" s="80" t="s">
+        <v>284</v>
+      </c>
+      <c r="W22" s="87" t="n">
         <f aca="false">SUM(W20:W21)</f>
-        <v>36</v>
-      </c>
-      <c r="X22" s="87" t="n">
+        <v>47</v>
+      </c>
+      <c r="X22" s="88" t="n">
         <f aca="false">W22/W2</f>
-        <v>0.654545454545455</v>
+        <v>0.854545454545455</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E23" s="83" t="s">
-        <v>272</v>
+      <c r="E23" s="84" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
